--- a/artfynd/A 5957-2026 artfynd.xlsx
+++ b/artfynd/A 5957-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119442798</v>
+        <v>119442359</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,30 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748901</v>
+        <v>748833</v>
       </c>
       <c r="R2" t="n">
-        <v>7154532</v>
+        <v>7154607</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119442395</v>
+        <v>119442582</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748844</v>
+        <v>748785</v>
       </c>
       <c r="R3" t="n">
-        <v>7154636</v>
+        <v>7154632</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119442850</v>
+        <v>119442832</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748896</v>
+        <v>748902</v>
       </c>
       <c r="R4" t="n">
-        <v>7154537</v>
+        <v>7154544</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119442832</v>
+        <v>119442395</v>
       </c>
       <c r="B5" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748902</v>
+        <v>748844</v>
       </c>
       <c r="R5" t="n">
-        <v>7154544</v>
+        <v>7154636</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,6 +1076,625 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119442404</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Eliasgrovliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>748821</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7154612</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119442417</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Eliasgrovliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>748818</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7154626</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119442425</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Eliasgrovliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>748799</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7154623</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>119442798</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Eliasgrovliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>748901</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7154532</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>119442569</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Eliasgrovliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>748794</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7154627</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>119442385</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Eliasgrovliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>748833</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7154607</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5957-2026 artfynd.xlsx
+++ b/artfynd/A 5957-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442359</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442582</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442832</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442395</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442404</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442417</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442425</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,6 +1524,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442798</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1593,6 +1638,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442569</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1695,8 +1745,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442385</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>